--- a/data/excel/VisaManualBooking.xlsx
+++ b/data/excel/VisaManualBooking.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6A3EFD-A4CD-462F-848B-1A16EBC2BF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBB10D0-D447-49E3-BE62-C31E367C0134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet6" sheetId="8" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="7" r:id="rId6"/>
+    <sheet name="VISABODC" sheetId="8" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="10" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="172">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -495,9 +496,6 @@
     <t>Verify manual booking for visa with 1 traveller</t>
   </si>
   <si>
-    <t>,test1@quadlabs.com,test2@quadlabs.com</t>
-  </si>
-  <si>
     <t>Verify manual booking for visa with 1 adult</t>
   </si>
   <si>
@@ -507,28 +505,43 @@
     <t>Verify manual booking for visa with 1 adult , 1 child and 1 infant</t>
   </si>
   <si>
-    <t>Password@@12</t>
-  </si>
-  <si>
-    <t>Test125@quadlabs.com</t>
-  </si>
-  <si>
-    <t>Test126@quadlabs.com</t>
-  </si>
-  <si>
-    <t>Test127@quadlabs.com</t>
-  </si>
-  <si>
     <t>EE6B4B@E7</t>
   </si>
   <si>
-    <t>Gaurav Shah,Sumit Shah</t>
-  </si>
-  <si>
     <t>2145786522G</t>
   </si>
   <si>
     <t>Akash001@quadlabs.com</t>
+  </si>
+  <si>
+    <t>Piyush_ql</t>
+  </si>
+  <si>
+    <t>Gaurav Dubey,Sumit Shah</t>
+  </si>
+  <si>
+    <t>5-Aug-2024,5-Feb-2023</t>
+  </si>
+  <si>
+    <t>2145426521G</t>
+  </si>
+  <si>
+    <t>Saurabh Dubey,Sunita Shah</t>
+  </si>
+  <si>
+    <t>Bal Krishna,Sumit Shah</t>
+  </si>
+  <si>
+    <t>2145786521F</t>
+  </si>
+  <si>
+    <t>2145786545V</t>
+  </si>
+  <si>
+    <t>750,JMD</t>
+  </si>
+  <si>
+    <t>Saurav Singh,Satish Shah</t>
   </si>
 </sst>
 </file>
@@ -623,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -638,6 +651,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2096,7 +2121,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -2107,11 +2132,11 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>97</v>
+      <c r="F2" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>106</v>
@@ -2302,7 +2327,7 @@
         <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -2508,7 +2533,7 @@
         <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -2711,11 +2736,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K4" xr:uid="{2BF9A17B-8264-4700-A928-A4DB336C1293}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{997C06AD-95DE-46E9-A103-AB8581E765AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E4" xr:uid="{997C06AD-95DE-46E9-A103-AB8581E765AB}">
       <formula1>"at,qlabs12345"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2:AQ4" xr:uid="{48DC80EE-CAF7-4D79-A049-4023D17DA3A8}">
@@ -2733,25 +2758,33 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4" xr:uid="{1A92AC22-4C0A-4434-BD25-EF2B8FFB8B65}">
       <formula1>"One Way,Round Trip"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{0F5C1780-0960-471C-8CF0-9D2144C9A77E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4" xr:uid="{0F5C1780-0960-471C-8CF0-9D2144C9A77E}">
       <formula1>"Piyush_QL,k.gaurav"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{EAE2826F-53AE-46A3-BEBA-3E124A03DCF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G4" xr:uid="{EAE2826F-53AE-46A3-BEBA-3E124A03DCF8}">
       <formula1>"Password@123456,Gaurav@130"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK4" xr:uid="{7EC555ED-E466-4962-B7C5-385F20953E65}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{21124DB8-3533-4652-96E4-FB7B1D6790CB}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{15530CDC-131E-4953-BD8C-9D131EB9AC58}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{4E60F982-FC22-44AF-A5C6-B69079A67F7B}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{3E59DFD6-1FBE-4DC0-BBB8-62E2CE361ED8}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{B75E25C0-195E-4B46-A3E1-F3E3E71DBED6}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{3FE8A31E-A084-4D53-8AD6-6500A8D37DC7}"/>
-    <hyperlink ref="F3" r:id="rId4" display="shubham.natkar@quadlabs.com" xr:uid="{F4DCBC23-1EAA-4CBC-BEC8-43D9C0967333}"/>
-    <hyperlink ref="F4" r:id="rId5" display="shubham.natkar@quadlabs.com" xr:uid="{8D4D5A83-6EF1-46E3-9C8D-2E95355B045A}"/>
-    <hyperlink ref="G3" r:id="rId6" display="Piyush@321" xr:uid="{41428C6E-5713-4D55-A0F1-1DFBDFE1031B}"/>
-    <hyperlink ref="G4" r:id="rId7" display="Piyush@321" xr:uid="{5A9B1097-E1B3-44A0-BD15-8E455252A79E}"/>
-    <hyperlink ref="H3:H4" r:id="rId8" display="ankit@quadlabs.com" xr:uid="{FB8EB32E-D085-45BF-8E12-C55A24892B4E}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{3FE8A31E-A084-4D53-8AD6-6500A8D37DC7}"/>
+    <hyperlink ref="F3" r:id="rId2" display="shubham.natkar@quadlabs.com" xr:uid="{F4DCBC23-1EAA-4CBC-BEC8-43D9C0967333}"/>
+    <hyperlink ref="F4" r:id="rId3" display="shubham.natkar@quadlabs.com" xr:uid="{8D4D5A83-6EF1-46E3-9C8D-2E95355B045A}"/>
+    <hyperlink ref="G3" r:id="rId4" display="Piyush@321" xr:uid="{41428C6E-5713-4D55-A0F1-1DFBDFE1031B}"/>
+    <hyperlink ref="G4" r:id="rId5" display="Piyush@321" xr:uid="{5A9B1097-E1B3-44A0-BD15-8E455252A79E}"/>
+    <hyperlink ref="H3:H4" r:id="rId6" display="ankit@quadlabs.com" xr:uid="{FB8EB32E-D085-45BF-8E12-C55A24892B4E}"/>
+    <hyperlink ref="G2" r:id="rId7" xr:uid="{D234737E-9966-4B59-9F24-68484B25EF1D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3263,6 +3296,334 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E7D4C-CFA8-4E33-B3E5-1039BED15766}">
+  <dimension ref="A1:AS2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="14">
+        <v>1</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0</v>
+      </c>
+      <c r="K2" s="14">
+        <v>0</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK2" s="14">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{D3C483E7-6091-45A4-8978-C97EE374BFB1}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{962F734B-CCE7-4F1E-8326-3508E16FE521}">
+      <formula1>"Tourist,Immigration,Student,Work permit,Employment,Dependent,Family visitor,Domestic Worker,Permanent migration,Business Visa"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2" xr:uid="{0390B823-91F3-4ACB-8367-5239634A1AA8}">
+      <formula1>"Single,Double,Multiple"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2" xr:uid="{4FA69C2A-C214-4DCF-A22C-FFB0797C51D8}">
+      <formula1>"ABC Supplier,Hotelbeds"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{22E3C3EE-5873-4FEA-B980-D1C6C4EE45F6}">
+      <formula1>"DOCS COLLECTED,DOCS UPLOADED,DOCS VERIFIED,VISA APPLIED,VISA APPROVED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{4B52C3D7-3E50-482C-8793-49FE835EEF5C}">
+      <formula1>"Male,Female,Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{1D32C22A-7AA1-4A3E-B49C-F5E728D0F981}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2" xr:uid="{00609531-B19F-4C6A-84BB-85928884A05A}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2" xr:uid="{4754D1F8-133F-4824-8603-090473EAC072}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{DD4C9E0A-0B94-4BF3-8C5D-E283BE955437}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{6BB3D70A-9E98-4032-B752-F7782E82DA35}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{EF9D39D4-35EC-4551-9F91-1555191C77A8}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{39A47EC8-3A92-4C98-86B6-FBAC8B1E024A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0B9580-7173-4D2C-9D88-EFAF0F7AF953}">
   <dimension ref="A1:AS4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3452,7 +3813,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -3463,13 +3824,13 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="F2" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>161</v>
       </c>
       <c r="I2" s="9">
@@ -3589,7 +3950,7 @@
         <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -3600,14 +3961,14 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="F3" s="13" t="s">
         <v>162</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -3726,7 +4087,7 @@
         <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -3737,14 +4098,14 @@
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>163</v>
+      <c r="F4" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -3860,7 +4221,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS4" xr:uid="{8557887D-D8C8-4A05-A01B-F78323A2BF89}">
       <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
     </dataValidation>
@@ -3888,368 +4249,954 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K4" xr:uid="{E5778879-254C-49BC-97FF-8FA1F2F3631D}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{B496BA27-4A93-49CA-A0E6-9B9D1423DDF0}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{86DF1FFF-3D0D-41D2-9F69-09488D5294D6}">
-      <formula1>"Piyush_QL"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{34B48CA6-559C-427C-B24A-2F4F118B90B9}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{35030481-2149-4E3B-A99F-0C0577158C8B}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{427A6AD3-7BEA-4ADE-AA68-DCEE76B837E1}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{DE990F2E-95BF-4EF6-98A5-AA662068AFCD}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Password@123" xr:uid="{16B0CFCB-C67D-42FD-B988-BC47F2C2607C}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{BF7542FB-658A-4A2E-AE35-8F3CBC3C7F4E}"/>
-    <hyperlink ref="F3" r:id="rId4" display="shubham.natkar@quadlabs.com" xr:uid="{4A79CE7A-0A94-4302-BD0F-B897EE49F652}"/>
-    <hyperlink ref="H3" r:id="rId5" xr:uid="{73912204-6FA4-4C77-86DF-140B2FACBDE6}"/>
-    <hyperlink ref="F4" r:id="rId6" display="shubham.natkar@quadlabs.com" xr:uid="{DEB9FD6F-AED2-4ACB-A99A-40AEFA28AA70}"/>
-    <hyperlink ref="H4" r:id="rId7" xr:uid="{1DC43618-3CB9-4894-BE5F-47B04187A46E}"/>
-    <hyperlink ref="G3" r:id="rId8" display="Password@123" xr:uid="{600E51D8-2533-4BDC-BF69-CDC5CA3264EE}"/>
-    <hyperlink ref="G4" r:id="rId9" display="Password@123" xr:uid="{C0B9A227-A7A2-42F4-B0BA-5C1577B15D33}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E7D4C-CFA8-4E33-B3E5-1039BED15766}">
-  <dimension ref="A1:AS2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI1" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO1" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="AQ1" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="AS1" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I2" s="9">
-        <v>1</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9">
-        <v>0</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="M2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>113</v>
-      </c>
-      <c r="R2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" t="s">
-        <v>118</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="W2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AI2">
-        <v>10</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="9">
-        <v>3</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO2" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{FD70B4C8-4F01-43D1-A539-1AF434661953}">
-      <formula1>"Piyush_QL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{5C2ADDA8-1ACD-4E49-8B3B-E89E549816A1}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{D3C483E7-6091-45A4-8978-C97EE374BFB1}">
-      <formula1>"0,1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{962F734B-CCE7-4F1E-8326-3508E16FE521}">
-      <formula1>"Tourist,Immigration,Student,Work permit,Employment,Dependent,Family visitor,Domestic Worker,Permanent migration,Business Visa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2" xr:uid="{0390B823-91F3-4ACB-8367-5239634A1AA8}">
-      <formula1>"Single,Double,Multiple"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2" xr:uid="{4FA69C2A-C214-4DCF-A22C-FFB0797C51D8}">
-      <formula1>"ABC Supplier,Hotelbeds"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{22E3C3EE-5873-4FEA-B980-D1C6C4EE45F6}">
-      <formula1>"DOCS COLLECTED,DOCS UPLOADED,DOCS VERIFIED,VISA APPLIED,VISA APPROVED"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{4B52C3D7-3E50-482C-8793-49FE835EEF5C}">
-      <formula1>"Male,Female,Others"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{1D32C22A-7AA1-4A3E-B49C-F5E728D0F981}">
-      <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2" xr:uid="{00609531-B19F-4C6A-84BB-85928884A05A}">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2" xr:uid="{4754D1F8-133F-4824-8603-090473EAC072}">
-      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{4FEE483C-2838-440E-9F9B-48B4B3D2D5B6}">
-      <formula1>"EE6B4B@E7,Ankur@12345,F1CD@9E4B"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{CB415AF1-D5D1-4AD7-9026-831AED4665EF}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{7697E5B2-5C84-4F1D-A590-66AD32D289AD}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{98D62CA2-7EC3-4B5F-B96C-DC1854A4A088}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{944EC520-550C-4462-AA56-786EEC1FB260}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{0A5294CD-4227-452E-9AB5-B460A61520CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46692D9-C129-4C4C-BC69-4E754DBB57AF}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A8DA5C4-A27D-41E9-B063-8DF3ABF270F0}">
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>156</v>
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="17">
+        <v>1</v>
+      </c>
+      <c r="J2" s="17">
+        <v>1</v>
+      </c>
+      <c r="K2" s="17">
+        <v>1</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK2" s="17">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{532BEA5C-B37F-405A-BD76-3398DAB8EA35}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{194C6D62-3FA6-43CE-A054-A3F0DB71084D}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{79D7C830-9E50-407D-B021-E0FB0C6F77FD}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{95F9E1B2-9404-4C64-A816-53C1D18AEBB5}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{1CB36E88-F98C-4677-8F48-04706762C040}">
+      <formula1>"Tourist,Immigration,Student,Work permit,Employment,Dependent,Family visitor,Domestic Worker,Permanent migration,Business Visa"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2" xr:uid="{1A2172AF-CEEF-4CD9-B87D-5BCA0AF9C8A2}">
+      <formula1>"Single,Double,Multiple"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2" xr:uid="{D3E71471-CE25-4BE9-9C16-9B4A0028F4C2}">
+      <formula1>"ABC Supplier,Hotelbeds"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{CC3D3CDA-111B-4635-BD7B-54ECDE32BAD9}">
+      <formula1>"DOCS COLLECTED,DOCS UPLOADED,DOCS VERIFIED,VISA APPLIED,VISA APPROVED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{BE2908B0-E24A-4298-8208-E7DF119534E5}">
+      <formula1>"Male,Female,Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{9148AD3D-02D7-4BDE-80BD-2D32A64ED50E}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2" xr:uid="{01F6C26B-AC54-4DE8-A04F-4B1C9B6B6B85}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2" xr:uid="{17950D35-92AA-42BB-AFB4-7DC40A3CDE97}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{E5F265F3-A041-4E64-B6D8-938A6D8DA515}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A611BD-A040-4F9B-ACF1-38DC0E4F6E56}">
+  <dimension ref="A1:AS4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="17">
+        <v>1</v>
+      </c>
+      <c r="J2" s="17">
+        <v>0</v>
+      </c>
+      <c r="K2" s="17">
+        <v>0</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK2" s="17">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I3" s="17">
+        <v>1</v>
+      </c>
+      <c r="J3" s="17">
+        <v>1</v>
+      </c>
+      <c r="K3" s="17">
+        <v>0</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK3" s="17">
+        <v>3</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="17">
+        <v>1</v>
+      </c>
+      <c r="J4" s="17">
+        <v>1</v>
+      </c>
+      <c r="K4" s="17">
+        <v>1</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U4" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK4" s="17">
+        <v>3</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO4" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{8873E7B0-B2AE-41D7-8176-3B434B100C00}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{8FD707C7-2619-4421-90F0-6FE6859932EF}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{BFAA7DF1-AF93-4B12-B085-E03F85986A8F}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K4" xr:uid="{66F68F63-EA59-4A09-9B7F-115D6D586766}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4" xr:uid="{FD0106D7-3138-4559-A75C-7AACAC97023F}">
+      <formula1>"Tourist,Immigration,Student,Work permit,Employment,Dependent,Family visitor,Domestic Worker,Permanent migration,Business Visa"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4" xr:uid="{E27B8745-18B6-4061-B392-CE051A153AB4}">
+      <formula1>"Single,Double,Multiple"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z4" xr:uid="{34EC863D-2A94-4C0A-B51D-6B642B080041}">
+      <formula1>"ABC Supplier,Hotelbeds"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA4" xr:uid="{DD543DCE-1A19-4F2A-941E-8C8E89FA6FE0}">
+      <formula1>"DOCS COLLECTED,DOCS UPLOADED,DOCS VERIFIED,VISA APPLIED,VISA APPROVED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4" xr:uid="{F3CC529E-CEE1-42F8-99C8-FA899185B423}">
+      <formula1>"Male,Female,Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK4" xr:uid="{7ADF5CBB-65A7-4B2E-8A1B-CFAD64F14918}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ4" xr:uid="{F142B5A0-A7F4-4996-BB34-283D6D866B75}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS4" xr:uid="{7B405C2E-EF15-41B5-8AFB-F476EB617928}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{19ED9F1C-07AB-484F-9D88-F6407863F147}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{D8E14215-1DCE-48CB-96B0-96AE5D0E5C0D}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{A4E2F2EC-4C0D-436B-8F94-00487D59F16F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/excel/VisaManualBooking.xlsx
+++ b/data/excel/VisaManualBooking.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBB10D0-D447-49E3-BE62-C31E367C0134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6DB371-17D0-4005-96B2-898CD30FD6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="172">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -61,12 +61,6 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Piyush_QL</t>
-  </si>
-  <si>
-    <t>Password@123456</t>
-  </si>
-  <si>
     <t>SelectClient</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
     <t>Cash</t>
   </si>
   <si>
-    <t>kapil.kumar@quadlabs.com</t>
-  </si>
-  <si>
     <t>TripType</t>
   </si>
   <si>
@@ -358,9 +349,6 @@
     <t>7777777104,7777777105,7777777106,8888888826,8888888827</t>
   </si>
   <si>
-    <t>Password@123</t>
-  </si>
-  <si>
     <t>CT</t>
   </si>
   <si>
@@ -454,9 +442,6 @@
     <t>Male</t>
   </si>
   <si>
-    <t>Test123@quadlabs.com</t>
-  </si>
-  <si>
     <t>Sanket Shah,Sumit Shah</t>
   </si>
   <si>
@@ -542,6 +527,21 @@
   </si>
   <si>
     <t>Saurav Singh,Satish Shah</t>
+  </si>
+  <si>
+    <t>E0@DA44FE</t>
+  </si>
+  <si>
+    <t>akshay.kumar@quadlabs.com</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RAVI.KUMAR@QLABS12345.com</t>
   </si>
 </sst>
 </file>
@@ -647,7 +647,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -663,6 +662,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1036,175 +1036,175 @@
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="V1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="AQ1" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="BG1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="BI1" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="BJ1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BK1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BL1" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="BK1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="BL1" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:64" x14ac:dyDescent="0.25">
@@ -1212,25 +1212,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>12</v>
+      <c r="F2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="I2" s="9">
         <v>2</v>
@@ -1242,154 +1242,154 @@
         <v>1</v>
       </c>
       <c r="L2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S2">
         <v>124578</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X2">
         <v>123</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>12</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB2">
         <v>14</v>
       </c>
       <c r="AC2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE2">
         <v>784521</v>
       </c>
       <c r="AF2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>123</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK2">
         <v>12</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM2">
         <v>14</v>
       </c>
       <c r="AN2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP2">
         <v>784541</v>
       </c>
       <c r="AQ2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR2">
         <v>100</v>
       </c>
       <c r="AS2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU2">
         <v>2</v>
       </c>
       <c r="AV2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX2">
         <v>100</v>
       </c>
       <c r="AY2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA2">
         <v>2</v>
       </c>
       <c r="BB2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD2">
         <v>100</v>
       </c>
       <c r="BE2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG2">
         <v>2</v>
       </c>
       <c r="BH2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ2">
         <v>30</v>
@@ -1398,7 +1398,7 @@
         <v>8888888819</v>
       </c>
       <c r="BL2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.25">
@@ -1406,25 +1406,25 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
+      <c r="F3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="I3" s="9">
         <v>2</v>
@@ -1436,154 +1436,154 @@
         <v>1</v>
       </c>
       <c r="L3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S3">
         <v>124578</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X3">
         <v>123</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z3">
         <v>12</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB3">
         <v>14</v>
       </c>
       <c r="AC3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3">
         <v>784521</v>
       </c>
       <c r="AF3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>123</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK3">
         <v>12</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM3">
         <v>14</v>
       </c>
       <c r="AN3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3">
         <v>784541</v>
       </c>
       <c r="AQ3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR3">
         <v>100</v>
       </c>
       <c r="AS3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU3">
         <v>2</v>
       </c>
       <c r="AV3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX3">
         <v>100</v>
       </c>
       <c r="AY3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA3">
         <v>2</v>
       </c>
       <c r="BB3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD3">
         <v>100</v>
       </c>
       <c r="BE3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG3">
         <v>2</v>
       </c>
       <c r="BH3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ3">
         <v>30</v>
@@ -1592,7 +1592,7 @@
         <v>8888888820</v>
       </c>
       <c r="BL3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.25">
@@ -1600,25 +1600,25 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
+      <c r="F4" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="I4" s="9">
         <v>2</v>
@@ -1630,154 +1630,154 @@
         <v>1</v>
       </c>
       <c r="L4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S4">
         <v>124578</v>
       </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X4">
         <v>123</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z4">
         <v>12</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB4">
         <v>14</v>
       </c>
       <c r="AC4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>784521</v>
       </c>
       <c r="AF4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>123</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK4">
         <v>12</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM4">
         <v>14</v>
       </c>
       <c r="AN4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP4">
         <v>784541</v>
       </c>
       <c r="AQ4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR4">
         <v>100</v>
       </c>
       <c r="AS4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU4">
         <v>2</v>
       </c>
       <c r="AV4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX4">
         <v>100</v>
       </c>
       <c r="AY4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA4">
         <v>2</v>
       </c>
       <c r="BB4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD4">
         <v>100</v>
       </c>
       <c r="BE4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG4">
         <v>2</v>
       </c>
       <c r="BH4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ4">
         <v>30</v>
@@ -1786,11 +1786,11 @@
         <v>8888888821</v>
       </c>
       <c r="BL4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4" xr:uid="{974C5DA5-2527-4143-A7C1-DB056CF21531}">
       <formula1>"One Way,Round Trip"</formula1>
     </dataValidation>
@@ -1806,32 +1806,35 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2:AQ4" xr:uid="{321C45C1-EF69-4D62-9D82-852799C85C30}">
       <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{42983C8C-45A6-4081-9916-68DD1BF75547}">
-      <formula1>"Password@123456"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{7DD99318-6E22-45F3-AAAC-CE64D68F2FE1}">
-      <formula1>"Piyush_QL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{2DC46BC7-2229-4720-9004-E750E91A69B1}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K4" xr:uid="{9672C72C-1C8B-45F3-8BE7-138E78F58A2C}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4" xr:uid="{856A8B3D-7C69-4EE8-88C0-AD31211CA45C}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{FFBE3E90-7F81-4930-9715-B6B60052E245}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{833EA324-411B-40BF-BEF7-EFE251AB7FCD}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{66588ABA-2FF8-4C39-BB19-6FA499B992FF}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{7EA71DE0-EE4F-46C9-BA15-17609478FA71}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{5FA9988C-AAB2-4B7F-9754-DD3CAC4AF8FE}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{12948124-8BAF-4E2E-9F94-CB2EB3ACA693}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{A8D5479C-98F9-4B18-8073-87407739638E}"/>
-    <hyperlink ref="F3" r:id="rId4" display="shubham.natkar@quadlabs.com" xr:uid="{D18CC0DB-AE72-427A-ABAB-7D01FADAC3C7}"/>
-    <hyperlink ref="G3" r:id="rId5" display="Piyush@321" xr:uid="{B591D4E4-E1D0-4F7E-B6AE-1E81F1FE9E8C}"/>
-    <hyperlink ref="H3" r:id="rId6" xr:uid="{CF8CAE88-729C-4DFF-802D-ED0138B93E76}"/>
-    <hyperlink ref="F4" r:id="rId7" display="shubham.natkar@quadlabs.com" xr:uid="{31A86C5C-F9F8-4758-80FF-D6D7E26CC24C}"/>
-    <hyperlink ref="G4" r:id="rId8" display="Piyush@321" xr:uid="{36233FAC-2A6A-4890-89D6-F0136D7E0A5B}"/>
-    <hyperlink ref="H4" r:id="rId9" xr:uid="{F60999E8-8128-46F3-98E1-624D0597CB30}"/>
+    <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{4084B9A6-E89E-4011-A72E-37B306EFD402}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{CDCD8313-6AE4-4C06-8348-8D6DCEA872B7}"/>
+    <hyperlink ref="H3" r:id="rId3" display="ankit@quadlabs.com" xr:uid="{C5F6CB75-688D-443B-B5E1-69B3DA1A4DDA}"/>
+    <hyperlink ref="G3" r:id="rId4" display="EE6B4B@E7" xr:uid="{7C8B078B-6DD0-430D-BA3C-AD338866BC4F}"/>
+    <hyperlink ref="H4" r:id="rId5" display="ankit@quadlabs.com" xr:uid="{EDDD0D07-DD46-42BF-B1C4-E5428B15F841}"/>
+    <hyperlink ref="G4" r:id="rId6" display="EE6B4B@E7" xr:uid="{47D40F60-96F0-43A9-B380-2023128C6FB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1933,187 +1936,187 @@
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="V1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="AQ1" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="BG1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="BI1" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="BJ1" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="BK1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BL1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="BM1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="BL1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="BM1" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="BN1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BO1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP1" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="BO1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="BP1" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.25">
@@ -2121,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -2132,14 +2135,14 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>159</v>
+      <c r="F2" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -2151,183 +2154,183 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S2">
         <v>124578</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X2">
         <v>123</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>12</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB2">
         <v>14</v>
       </c>
       <c r="AC2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE2">
         <v>784521</v>
       </c>
       <c r="AF2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>123</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK2">
         <v>12</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM2">
         <v>14</v>
       </c>
       <c r="AN2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP2">
         <v>784541</v>
       </c>
       <c r="AQ2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR2">
         <v>100</v>
       </c>
       <c r="AS2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU2">
         <v>2</v>
       </c>
       <c r="AV2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX2">
         <v>100</v>
       </c>
       <c r="AY2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA2">
         <v>2</v>
       </c>
       <c r="BB2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD2">
         <v>100</v>
       </c>
       <c r="BE2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG2">
         <v>2</v>
       </c>
       <c r="BH2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BK2" s="9">
         <v>3</v>
       </c>
       <c r="BL2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BM2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="BN2">
         <v>30</v>
       </c>
       <c r="BO2" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="BP2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -2339,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -2357,183 +2360,183 @@
         <v>0</v>
       </c>
       <c r="L3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S3">
         <v>124578</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X3">
         <v>123</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z3">
         <v>12</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB3">
         <v>14</v>
       </c>
       <c r="AC3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3">
         <v>784521</v>
       </c>
       <c r="AF3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>123</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK3">
         <v>12</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM3">
         <v>14</v>
       </c>
       <c r="AN3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3">
         <v>784541</v>
       </c>
       <c r="AQ3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR3">
         <v>100</v>
       </c>
       <c r="AS3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU3">
         <v>2</v>
       </c>
       <c r="AV3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX3">
         <v>100</v>
       </c>
       <c r="AY3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA3">
         <v>2</v>
       </c>
       <c r="BB3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD3">
         <v>100</v>
       </c>
       <c r="BE3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG3">
         <v>2</v>
       </c>
       <c r="BH3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BK3" s="9">
         <v>1</v>
       </c>
       <c r="BL3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM3" t="s">
         <v>101</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>104</v>
       </c>
       <c r="BN3">
         <v>30</v>
       </c>
       <c r="BO3" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BP3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -2545,13 +2548,13 @@
         <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -2563,175 +2566,175 @@
         <v>1</v>
       </c>
       <c r="L4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S4">
         <v>124578</v>
       </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X4">
         <v>123</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z4">
         <v>12</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB4">
         <v>14</v>
       </c>
       <c r="AC4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>784521</v>
       </c>
       <c r="AF4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>123</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AK4">
         <v>12</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AM4">
         <v>14</v>
       </c>
       <c r="AN4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP4">
         <v>784541</v>
       </c>
       <c r="AQ4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR4">
         <v>100</v>
       </c>
       <c r="AS4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU4">
         <v>2</v>
       </c>
       <c r="AV4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX4">
         <v>100</v>
       </c>
       <c r="AY4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA4">
         <v>2</v>
       </c>
       <c r="BB4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD4">
         <v>100</v>
       </c>
       <c r="BE4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG4">
         <v>2</v>
       </c>
       <c r="BH4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BI4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BJ4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BK4" s="9">
         <v>2</v>
       </c>
       <c r="BL4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BM4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BN4">
         <v>30</v>
       </c>
       <c r="BO4" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="BP4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2792,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83380B9A-3A43-48DF-97E8-1ED12D260582}">
-  <dimension ref="A1:AS3"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -2859,118 +2862,118 @@
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="W1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="V1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="AO1" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AP1" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="AQ1" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="AS1" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -2978,25 +2981,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
+      <c r="F2" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>142</v>
+        <v>167</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>171</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3008,288 +3011,156 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" t="s">
         <v>113</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>114</v>
       </c>
-      <c r="S2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="W2" t="s">
         <v>118</v>
       </c>
-      <c r="U2" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="7" t="s">
+      <c r="X2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
         <v>137</v>
       </c>
-      <c r="W2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>141</v>
-      </c>
       <c r="AH2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI2">
         <v>10</v>
       </c>
       <c r="AJ2" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="AK2" s="9">
         <v>3</v>
       </c>
       <c r="AL2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AP2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>1</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R3" t="s">
-        <v>114</v>
-      </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>118</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="W3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>145</v>
-      </c>
-      <c r="AI3">
-        <v>10</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK3" s="9">
-        <v>3</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>151</v>
-      </c>
-      <c r="AO3" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>153</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{73004538-1CB2-46FA-AD1C-C9C6D8A6961A}">
-      <formula1>"Piyush_QL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3" xr:uid="{9F1B74FA-8E9C-481E-AA3B-37685FC56AC0}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K3" xr:uid="{914EF4F6-49B8-4827-A015-B0B34767C3BC}">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{914EF4F6-49B8-4827-A015-B0B34767C3BC}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3" xr:uid="{3F6BD7AA-CBF5-44E1-A4B7-CF035CE3D249}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{3F6BD7AA-CBF5-44E1-A4B7-CF035CE3D249}">
       <formula1>"Tourist,Immigration,Student,Work permit,Employment,Dependent,Family visitor,Domestic Worker,Permanent migration,Business Visa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3" xr:uid="{19381C60-1D16-4F87-A405-96A0A56C84E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2" xr:uid="{19381C60-1D16-4F87-A405-96A0A56C84E4}">
       <formula1>"Single,Double,Multiple"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3" xr:uid="{478F349B-7030-4BE2-90C4-FE167389141C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2" xr:uid="{478F349B-7030-4BE2-90C4-FE167389141C}">
       <formula1>"ABC Supplier,Hotelbeds"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3" xr:uid="{FA4C7249-F127-47BD-B813-95CFDE27CC1C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2" xr:uid="{FA4C7249-F127-47BD-B813-95CFDE27CC1C}">
       <formula1>"DOCS COLLECTED,DOCS UPLOADED,DOCS VERIFIED,VISA APPLIED,VISA APPROVED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG3" xr:uid="{E93C7F57-04AF-41FE-A430-8008CE158A85}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{E93C7F57-04AF-41FE-A430-8008CE158A85}">
       <formula1>"Male,Female,Others"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK3" xr:uid="{49152DE4-F561-472E-9C32-5088ACEAFCCC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{49152DE4-F561-472E-9C32-5088ACEAFCCC}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3" xr:uid="{ADFBD08B-AB9B-4E52-81C3-1A22D7BAC6AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2" xr:uid="{ADFBD08B-AB9B-4E52-81C3-1A22D7BAC6AB}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3" xr:uid="{1A4C7555-1ABD-4D41-BF52-BC5609D985A8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2" xr:uid="{1A4C7555-1ABD-4D41-BF52-BC5609D985A8}">
       <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{CD7A95ED-068B-4FF1-AB35-5174B4B99E33}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{EC1FDAFF-060D-424E-87FB-119C05CFBA2F}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{B5031B0F-BC77-428F-B258-B8D9B7B303F4}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{BFA4C8AF-29E6-4CDC-8836-ECFAD0728C5B}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{40F8C29D-1071-40AF-9A3F-300AFAD869EF}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{8484B50F-170E-4A4F-85CA-29B5A0948B11}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{B380F217-FC74-4AD6-9708-3DDA40EA5123}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{9502C8C7-0201-4C1E-A300-B51A370D4F32}"/>
-    <hyperlink ref="F3" r:id="rId4" display="shubham.natkar@quadlabs.com" xr:uid="{F9F863DD-C02F-4658-9448-0CEDB7A027E5}"/>
-    <hyperlink ref="G3" r:id="rId5" xr:uid="{8F60BD99-3FE5-4880-BB79-F01EA588DAFB}"/>
-    <hyperlink ref="H3" r:id="rId6" xr:uid="{95B8DB62-C630-431D-904B-9DB9D49B72CC}"/>
+    <hyperlink ref="G2" r:id="rId1" display="EE6B4B@E7" xr:uid="{7685A8C8-BC24-4E1B-80CE-DFC9E7E2E3EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3326,118 +3197,118 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="AO1" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AQ1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="AS1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -3445,7 +3316,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -3456,125 +3327,125 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>159</v>
+      <c r="F2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="14">
+        <v>156</v>
+      </c>
+      <c r="I2" s="13">
         <v>1</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>0</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>0</v>
       </c>
-      <c r="L2" s="14" t="s">
-        <v>163</v>
+      <c r="L2" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="15" t="s">
+      <c r="X2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="3">
         <v>10</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="14">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="13">
         <v>3</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3694,118 +3565,118 @@
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="W1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="V1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="AO1" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AP1" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="AQ1" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="AS1" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -3813,7 +3684,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -3824,14 +3695,14 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>161</v>
+      <c r="F2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>156</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3843,114 +3714,114 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" t="s">
         <v>113</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>114</v>
       </c>
-      <c r="S2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="W2" t="s">
         <v>118</v>
       </c>
-      <c r="U2" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="7" t="s">
+      <c r="X2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
         <v>137</v>
       </c>
-      <c r="W2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>141</v>
-      </c>
       <c r="AH2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI2">
         <v>10</v>
       </c>
       <c r="AJ2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="9">
         <v>3</v>
       </c>
       <c r="AL2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AP2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -3961,14 +3832,14 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>159</v>
+      <c r="F3" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -3980,114 +3851,114 @@
         <v>0</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S3" t="s">
         <v>113</v>
       </c>
-      <c r="R3" t="s">
+      <c r="T3" t="s">
         <v>114</v>
       </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="U3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="W3" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG3" t="s">
         <v>137</v>
       </c>
-      <c r="W3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI3">
         <v>10</v>
       </c>
       <c r="AJ3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK3" s="9">
         <v>3</v>
       </c>
       <c r="AL3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AP3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -4098,14 +3969,14 @@
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>159</v>
+      <c r="F4" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -4117,106 +3988,106 @@
         <v>1</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="Q4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R4" t="s">
+        <v>110</v>
+      </c>
+      <c r="S4" t="s">
         <v>113</v>
       </c>
-      <c r="R4" t="s">
+      <c r="T4" t="s">
         <v>114</v>
       </c>
-      <c r="S4" t="s">
-        <v>117</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="U4" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="W4" t="s">
         <v>118</v>
       </c>
-      <c r="U4" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="V4" s="7" t="s">
+      <c r="X4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG4" t="s">
         <v>137</v>
       </c>
-      <c r="W4" t="s">
-        <v>122</v>
-      </c>
-      <c r="X4" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>141</v>
-      </c>
       <c r="AH4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI4">
         <v>10</v>
       </c>
       <c r="AJ4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK4" s="9">
         <v>3</v>
       </c>
       <c r="AL4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AO4" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AP4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4263,6 +4134,7 @@
     <hyperlink ref="G2" r:id="rId1" xr:uid="{98D62CA2-7EC3-4B5F-B96C-DC1854A4A088}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{944EC520-550C-4462-AA56-786EEC1FB260}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{0A5294CD-4227-452E-9AB5-B460A61520CB}"/>
+    <hyperlink ref="H2" r:id="rId4" xr:uid="{8B5B4584-7622-4A32-8AF8-54AF700B9EF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4300,126 +4172,126 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="AO1" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AQ1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="AS1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -4430,125 +4302,125 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="16" t="s">
+      <c r="F2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="16">
+        <v>1</v>
+      </c>
+      <c r="J2" s="16">
+        <v>1</v>
+      </c>
+      <c r="K2" s="16">
+        <v>1</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="17">
-        <v>1</v>
-      </c>
-      <c r="J2" s="17">
-        <v>1</v>
-      </c>
-      <c r="K2" s="17">
-        <v>1</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="Q2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="15" t="s">
+      <c r="X2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="3">
         <v>10</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="17">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="16">
         <v>3</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4628,118 +4500,118 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="Q1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="AO1" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AQ1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="AS1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -4747,7 +4619,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -4758,133 +4630,133 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>159</v>
+      <c r="F2" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="17">
+        <v>156</v>
+      </c>
+      <c r="I2" s="16">
         <v>1</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="16">
         <v>0</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="16">
         <v>0</v>
       </c>
-      <c r="L2" s="17" t="s">
-        <v>163</v>
+      <c r="L2" s="16" t="s">
+        <v>158</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="Q2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="15" t="s">
+      <c r="X2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="3">
         <v>10</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="17">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="16">
         <v>3</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>154</v>
+        <v>163</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -4895,133 +4767,133 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="16">
+        <v>1</v>
+      </c>
+      <c r="J3" s="16">
+        <v>1</v>
+      </c>
+      <c r="K3" s="16">
+        <v>0</v>
+      </c>
+      <c r="L3" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="17">
-        <v>1</v>
-      </c>
-      <c r="J3" s="17">
-        <v>1</v>
-      </c>
-      <c r="K3" s="17">
-        <v>0</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="V3" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="V3" s="15" t="s">
+      <c r="X3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH3" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI3" s="3">
         <v>10</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK3" s="17">
+        <v>27</v>
+      </c>
+      <c r="AK3" s="16">
         <v>3</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>154</v>
+        <v>164</v>
+      </c>
+      <c r="AO3" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ3" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS3" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -5032,125 +4904,125 @@
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="F4" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I4" s="16">
+        <v>1</v>
+      </c>
+      <c r="J4" s="16">
+        <v>1</v>
+      </c>
+      <c r="K4" s="16">
+        <v>1</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" s="17">
-        <v>1</v>
-      </c>
-      <c r="J4" s="17">
-        <v>1</v>
-      </c>
-      <c r="K4" s="17">
-        <v>1</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="Q4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="V4" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="U4" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="V4" s="15" t="s">
+      <c r="X4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="AH4" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AI4" s="3">
         <v>10</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK4" s="17">
+        <v>27</v>
+      </c>
+      <c r="AK4" s="16">
         <v>3</v>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO4" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
+      </c>
+      <c r="AO4" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AS4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
